--- a/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Templado" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Moldeado" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Templado" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moldeado" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Templado'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Moldeado'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -144,54 +152,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -551,15 +570,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -567,6 +587,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -595,9 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -626,8 +645,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -636,18 +672,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,6 +700,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -803,6 +840,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -942,6 +980,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1062,6 +1101,7 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
@@ -1181,6 +1221,26 @@
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>COUNTIF(E6:E32,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>COUNTIF(B6:B32,"?*")</f>
+        <v>21.0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -1207,12 +1267,26 @@
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A27:G27"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G32">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E29 E30 E31 E32" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1221,18 +1295,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1249,6 +1323,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1483,6 +1558,7 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -1660,6 +1736,7 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
@@ -1779,6 +1856,26 @@
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>COUNTIF(E6:E32,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>COUNTIF(B6:B32,"?*")</f>
+        <v>23.0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -1804,11 +1901,25 @@
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A27:G27"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G32">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
@@ -90,7 +90,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -127,8 +127,13 @@
         <bgColor rgb="00E0F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -150,11 +155,55 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,6 +245,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -572,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -647,9 +707,45 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Templado y conservación:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ Antes de templar se comprueba el AIRE del obrador: 18-20 °C y menos del 60 % de humedad. Las tres curvas de cobertura de esta hoja sólo funcionan dentro de esa ventana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «Moldeado» tienes una tabla editable de vida útil por familia: ajústala a tu fórmula. Está fuera del contador porque es una referencia, no una tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>▸ El chocolate acabado NO se congela: al descongelar condensa, el agua disuelve el azúcar de la superficie y deja sugar bloom. Sólo el granel de ganache admite congelación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -674,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -808,7 +904,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Pesar cobertura según orden de producción del día</t>
+          <t>Comprobar la temperatura y la humedad del obrador ANTES de templar: objetivo 18-20 °C y menos del 60 % de humedad (por encima, la manteca no cristaliza y aparece bloom) — anota la lectura: ____ °C</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -827,12 +923,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Trocear cobertura y colocar en temperadora</t>
+          <t>Pesar cobertura según orden de producción del día</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Templado</t>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -840,77 +936,77 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Trocear cobertura y colocar en temperadora</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Templado</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="13" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Proceso de templado — Chocolate negro</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Fundir a 50-55°C — registrar temperatura</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Templado</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Enfriar a 27-28°C sobre mármol o por siembra</t>
+          <t>Fundir a 50-55 °C — registrar temperatura</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -925,11 +1021,11 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Recalentar a 31-32°C — punto de trabajo</t>
+          <t>Enfriar a 27-28 °C sobre mármol o por siembra</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -944,11 +1040,11 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Test de templado: brillo, snap, contracción en molde</t>
+          <t>Recalentar a 31-32 °C — punto de trabajo</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -963,16 +1059,16 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Registrar lote, hora y temperatura final</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Test de templado en punta de espátula: debe secar en 3-5 min a 20 °C, con brillo, snap seco y contracción en el molde. Si no, volver a fundir y templar — no se moldea «a ver si sale»</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Templado</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -980,77 +1076,77 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Registrar lote, hora y temperatura final</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Proceso de templado — Chocolate con leche</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Fundir a 45-50°C — registrar temperatura</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>Templado</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Enfriar a 26-27°C sobre mármol o por siembra</t>
+          <t>Fundir a 45-50 °C — registrar temperatura</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -1065,11 +1161,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Recalentar a 29-30°C — punto de trabajo</t>
+          <t>Enfriar a 26-27 °C sobre mármol o por siembra</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -1084,16 +1180,16 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Test de templado y registrar lote</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Recalentar a 29-30 °C — punto de trabajo</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Templado</t>
         </is>
       </c>
       <c r="D25" s="11" t="n"/>
@@ -1101,77 +1197,77 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Test de templado en capa fina sobre papel: a 18-20 °C debe cristalizar en 3-5 min, con brillo uniforme y sin vetas, partiendo del punto de trabajo de 29-30 °C. Si no, volver a fundir y retemplar — no se moldea «a ver si sale». Registrar el lote, la hora y la temperatura final</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Proceso de templado — Chocolate blanco</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Fundir a 40-45°C — registrar temperatura</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Templado</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Enfriar a 25-26°C sobre mármol o por siembra</t>
+          <t>Fundir a 40-45 °C — registrar temperatura</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -1186,11 +1282,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Recalentar a 27-28°C — punto de trabajo</t>
+          <t>Enfriar a 25-26 °C sobre mármol o por siembra</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -1205,16 +1301,16 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Test de templado y registrar lote</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Recalentar a 28-29 °C — punto de trabajo</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Templado</t>
         </is>
       </c>
       <c r="D32" s="11" t="n"/>
@@ -1223,58 +1319,77 @@
       <c r="G32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="18" t="inlineStr">
+      <c r="A33" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Test de templado en capa fina sobre papel: a 18-20 °C debe cristalizar en 3-5 min, con brillo uniforme y sin vetas, partiendo del punto de trabajo de 28-29 °C. Si no, volver a fundir y retemplar — no se moldea «a ver si sale». Registrar el lote, la hora y la temperatura final</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C33">
-        <f>COUNTIF(E6:E32,"✓")</f>
-        <v>3.0</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34">
+        <f>COUNTIFS(B6:B33,"?*",E6:E33,"✓")-COUNTIFS(B6:B33,"Tarea",E6:E33,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E33">
-        <f>COUNTIF(B6:B32,"?*")</f>
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E34">
+        <f>COUNTIF(B6:B33,"?*")-COUNTIF(B6:B33,"Tarea")-COUNTIF(E6:E33,"N/A")</f>
+        <v>19.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G32">
+  <conditionalFormatting sqref="A6:G33">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26 E30 E31 E32 E33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1297,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1374,7 +1489,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Preparar moldes limpios y a temperatura ambiente (20-22°C)</t>
+          <t>Preparar moldes limpios y a temperatura ambiente (20-22 °C)</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1450,7 +1565,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Enfriar en cámara a 12-14°C durante 10-15 min</t>
+          <t>Enfriar en cámara a 12-14 °C durante 10-15 min</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -1685,7 +1800,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Enfriar en cámara a 12-14°C durante 20-30 min</t>
+          <t>Enfriar en cámara a 12-14 °C durante 20-30 min</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -1825,7 +1940,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Registrar mermas y chocolate descartado</t>
+          <t>Etiquetar cada lote con fecha de producción y consumo preferente según su familia (tabla al pie de la hoja)</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -1844,12 +1959,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Almacenar producto terminado a 15-18°C</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Conservación</t>
+          <t>Anotar las mermas del día: producto, cantidad y motivo (rotura, mal templado, bloom, prueba). El chocolate sin relleno y sin contaminar se puede refundir; el que lleva ganache o fruta, a residuo</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D32" s="11" t="n"/>
@@ -1858,57 +1973,329 @@
       <c r="G32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="18" t="inlineStr">
+      <c r="A33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Almacenar el producto terminado a 15-18 °C y 50-60 % de humedad, en oscuridad y lejos de olores fuertes (el cacao los absorbe) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Conservación</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C33">
-        <f>COUNTIF(E6:E32,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34">
+        <f>COUNTIFS(B6:B33,"?*",E6:E33,"✓")-COUNTIFS(B6:B33,"Tarea",E6:E33,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E33">
-        <f>COUNTIF(B6:B32,"?*")</f>
-        <v>23.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E34">
+        <f>COUNTIF(B6:B33,"?*")-COUNTIF(B6:B33,"Tarea")-COUNTIF(E6:E33,"N/A")</f>
+        <v>22.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL Y CONSERVACIÓN ORIENTATIVAS A 15-18 °C Y 50-60 % DE HUMEDAD — ajústala a tu fórmula y a tu obrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Tabletas y chocolate sin relleno</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>12-18 meses</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>El enemigo no es el tiempo: es la humedad, la luz y los olores. Sellado y en oscuridad</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Figuras huecas y piezas macizas</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>6-12 meses</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Igual que la tableta, pero la pieza hueca se raja con los cambios bruscos de temperatura</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="20" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>Bombones de ganache con nata fresca</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>10-15 días</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Actividad de agua alta: en refrigeración a 0-4 °C y atemperar CERRADOS antes de abrir, o condensan</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="20" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Bombones de ganache con nata UHT, sorbato o alcohol</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>4-8 semanas</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>El conservante y el alcohol bajan la actividad de agua; sin ellos no se llega ni a la mitad</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="20" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>2-4 meses</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>La grasa del fruto seco se enrancia y el frío no lo evita: manda la fecha, no el aspecto</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="20" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Trufas y rocas recubiertas</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>3-4 semanas</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Si llevan nata o mantequilla, se cuentan como ganache fresca</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="20" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Bombones de licor y cristalizados</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>3-6 meses</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>Vigilar la cristalización del azúcar en la cáscara: revienta y gotea</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="20" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Frutos secos garrapiñados y frutas confitadas bañadas</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>1-3 meses</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Se apelmazan con la humedad; envasado hermético con desecante si tu obrador es húmedo</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="20" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>Barquillos y crujientes bañados</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>3-4 semanas</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Pierden el crujiente mucho antes que la seguridad: se retiran por calidad</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="19" t="n"/>
+      <c r="G47" s="20" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>Chocolate acabado: NO congelar</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Nunca</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Al descongelar condensa, el agua disuelve el azúcar de la superficie y deja sugar bloom. Sólo el granel de ganache admite ≤ −18 °C 1-2 meses, descongelado 24 h en cámara y sin abrir</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="20" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="19">
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D47:G47"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D40:G40"/>
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D43:G43"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G32">
+  <conditionalFormatting sqref="A6:G33">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32 E33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
@@ -1378,8 +1378,8 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G33">
@@ -2270,8 +2270,8 @@
   <mergeCells count="19">
     <mergeCell ref="D44:G44"/>
     <mergeCell ref="A49:G49"/>
+    <mergeCell ref="D38:G38"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D38:G38"/>
     <mergeCell ref="D48:G48"/>
     <mergeCell ref="D41:G41"/>
     <mergeCell ref="A37:G37"/>
@@ -2282,8 +2282,8 @@
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="D46:G46"/>
     <mergeCell ref="D40:G40"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A27:G27"/>
     <mergeCell ref="D42:G42"/>
     <mergeCell ref="D39:G39"/>
     <mergeCell ref="D43:G43"/>
